--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B486"/>
+  <dimension ref="A1:B489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5290,6 +5290,36 @@
         <v>-221.499</v>
       </c>
     </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>3967.047</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>-3849.539</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>5168.991</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B489"/>
+  <dimension ref="A1:B490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5320,6 +5320,16 @@
         <v>5168.991</v>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>7230.551</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B490"/>
+  <dimension ref="A1:B491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5330,6 +5330,16 @@
         <v>7230.551</v>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>-2249.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B491"/>
+  <dimension ref="A1:B492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5340,6 +5340,16 @@
         <v>-2249.55</v>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>-5329.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B492"/>
+  <dimension ref="A1:B493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5350,6 +5350,16 @@
         <v>-5329.52</v>
       </c>
     </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>-4298.719</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B493"/>
+  <dimension ref="A1:B494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5360,6 +5360,16 @@
         <v>-4298.719</v>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>-2761.223</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B494"/>
+  <dimension ref="A1:B495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5370,6 +5370,16 @@
         <v>-2761.223</v>
       </c>
     </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>1226.669</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B495"/>
+  <dimension ref="A1:B498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5380,6 +5380,36 @@
         <v>1226.669</v>
       </c>
     </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>7712.123</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>8692.965</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>978.585</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B498"/>
+  <dimension ref="A1:B499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5410,6 +5410,16 @@
         <v>978.585</v>
       </c>
     </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>-4133.455</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B499"/>
+  <dimension ref="A1:B500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5420,6 +5420,16 @@
         <v>-4133.455</v>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>-5479.588</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B500"/>
+  <dimension ref="A1:B501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5430,6 +5430,16 @@
         <v>-5479.588</v>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>-7909.655</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B501"/>
+  <dimension ref="A1:B502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5440,6 +5440,16 @@
         <v>-7909.655</v>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>-360.196</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B502"/>
+  <dimension ref="A1:B503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5450,6 +5450,16 @@
         <v>-360.196</v>
       </c>
     </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>-1157.203</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B503"/>
+  <dimension ref="A1:B504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5460,6 +5460,16 @@
         <v>-1157.203</v>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>-10.188</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B504"/>
+  <dimension ref="A1:B505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5470,6 +5470,16 @@
         <v>-10.188</v>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>-1651.349</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B505"/>
+  <dimension ref="A1:B506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5480,6 +5480,16 @@
         <v>-1651.349</v>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>-219.786</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B506"/>
+  <dimension ref="A1:B508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5490,6 +5490,26 @@
         <v>-219.786</v>
       </c>
     </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>-9235.639999999999</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>-6066.627</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B508"/>
+  <dimension ref="A1:B509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5510,6 +5510,16 @@
         <v>-6066.627</v>
       </c>
     </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>6283.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B509"/>
+  <dimension ref="A1:B510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5520,6 +5520,16 @@
         <v>6283.3</v>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>-3147.265</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B510"/>
+  <dimension ref="A1:B511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5530,6 +5530,16 @@
         <v>-3147.265</v>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>-7454.663</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>-7454.663</v>
+        <v>-8167.432</v>
       </c>
     </row>
   </sheetData>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B511"/>
+  <dimension ref="A1:B512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5540,6 +5540,16 @@
         <v>-8167.432</v>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>4968.315</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5550,6 +5550,16 @@
         <v>4968.315</v>
       </c>
     </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>204.999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5560,6 +5560,36 @@
         <v>204.999</v>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>2335.17</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>-4124.514</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>-5688.481</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B516"/>
+  <dimension ref="A1:B517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5590,6 +5590,16 @@
         <v>-5688.481</v>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>117.629</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5600,6 +5600,16 @@
         <v>117.629</v>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>-2088.303</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B518"/>
+  <dimension ref="A1:B519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5610,6 +5610,16 @@
         <v>-2088.303</v>
       </c>
     </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>-2008.114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B519"/>
+  <dimension ref="A1:B520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5620,6 +5620,16 @@
         <v>-2008.114</v>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>-2477.128</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B520"/>
+  <dimension ref="A1:B521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5630,6 +5630,16 @@
         <v>-2477.128</v>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>1296.021</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B521"/>
+  <dimension ref="A1:B522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5640,6 +5640,16 @@
         <v>1296.021</v>
       </c>
     </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>-3150.414</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B522"/>
+  <dimension ref="A1:B523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5650,6 +5650,16 @@
         <v>-3150.414</v>
       </c>
     </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>3884.676</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B523"/>
+  <dimension ref="A1:B524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5660,6 +5660,16 @@
         <v>3884.676</v>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>7162.119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B524"/>
+  <dimension ref="A1:B525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5670,6 +5670,16 @@
         <v>7162.119</v>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>3678.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B525"/>
+  <dimension ref="A1:B526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5680,6 +5680,16 @@
         <v>3678.95</v>
       </c>
     </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>-417.526</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B526"/>
+  <dimension ref="A1:B527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5690,6 +5690,16 @@
         <v>-417.526</v>
       </c>
     </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>6381.069</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B527"/>
+  <dimension ref="A1:B529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5700,6 +5700,26 @@
         <v>6381.069</v>
       </c>
     </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>3290.898</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>5910.486</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5720,6 +5720,16 @@
         <v>5910.486</v>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>-3210.428</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5730,6 +5730,16 @@
         <v>-3210.428</v>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>-5043.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5740,6 +5740,26 @@
         <v>-5043.48</v>
       </c>
     </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>2438.4</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>3456.771</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B533"/>
+  <dimension ref="A1:B535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5760,6 +5760,26 @@
         <v>3456.771</v>
       </c>
     </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>1567.599</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>691.825</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B535"/>
+  <dimension ref="A1:B536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5780,6 +5780,16 @@
         <v>691.825</v>
       </c>
     </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>2543.352</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B536"/>
+  <dimension ref="A1:B538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5790,6 +5790,26 @@
         <v>2543.352</v>
       </c>
     </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>2668.488</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>2691.466</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B538"/>
+  <dimension ref="A1:B540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5810,6 +5810,26 @@
         <v>2691.466</v>
       </c>
     </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>-2294.609</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>-1356.705</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B540"/>
+  <dimension ref="A1:B541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5830,6 +5830,16 @@
         <v>-1356.705</v>
       </c>
     </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>-737.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B541"/>
+  <dimension ref="A1:B543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5840,6 +5840,26 @@
         <v>-737.48</v>
       </c>
     </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>2364.046</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>-943.2089999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B543"/>
+  <dimension ref="A1:B545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5860,6 +5860,26 @@
         <v>-943.2089999999999</v>
       </c>
     </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>109.426</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-2412.585</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B545"/>
+  <dimension ref="A1:B546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5880,6 +5880,16 @@
         <v>-2412.585</v>
       </c>
     </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>-3405.615</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B546"/>
+  <dimension ref="A1:B548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5890,6 +5890,26 @@
         <v>-3405.615</v>
       </c>
     </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>1041.241</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>1722.498</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B548"/>
+  <dimension ref="A1:B550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5910,6 +5910,26 @@
         <v>1722.498</v>
       </c>
     </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>-2701.242</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>134.512</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B550"/>
+  <dimension ref="A1:B554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5930,6 +5930,46 @@
         <v>134.512</v>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>6601.408</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>-2207.97</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>-1751.423</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>4780.698</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B554"/>
+  <dimension ref="A1:B558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5970,6 +5970,46 @@
         <v>4780.698</v>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>3170.879</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>-3836.118</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>5271.424</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>2231.081</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B558"/>
+  <dimension ref="A1:B559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6010,6 +6010,16 @@
         <v>2231.081</v>
       </c>
     </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>-53.265</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B559"/>
+  <dimension ref="A1:B560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6020,6 +6020,16 @@
         <v>-53.265</v>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>8016.652</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B560"/>
+  <dimension ref="A1:B561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6030,6 +6030,16 @@
         <v>8016.652</v>
       </c>
     </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>3037.692</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B561"/>
+  <dimension ref="A1:B563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6040,6 +6040,26 @@
         <v>3037.692</v>
       </c>
     </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>-214.171</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>2667.649</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B563"/>
+  <dimension ref="A1:B566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6060,6 +6060,36 @@
         <v>2667.649</v>
       </c>
     </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>42.611</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>-3406.842</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>-1957.913</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B566"/>
+  <dimension ref="A1:B567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6090,6 +6090,16 @@
         <v>-1957.913</v>
       </c>
     </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>307.996</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B567"/>
+  <dimension ref="A1:B568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6100,6 +6100,16 @@
         <v>307.996</v>
       </c>
     </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>7923.705</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B568"/>
+  <dimension ref="A1:B569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6110,6 +6110,16 @@
         <v>7923.705</v>
       </c>
     </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>6515.412</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B569"/>
+  <dimension ref="A1:B570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6120,6 +6120,16 @@
         <v>6515.412</v>
       </c>
     </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>567.814</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B570"/>
+  <dimension ref="A1:B571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6130,6 +6130,16 @@
         <v>567.814</v>
       </c>
     </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>-3519.234</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B571"/>
+  <dimension ref="A1:B573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6140,6 +6140,26 @@
         <v>-3519.234</v>
       </c>
     </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>-1888.259</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>11.014</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6160,6 +6160,66 @@
         <v>11.014</v>
       </c>
     </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>-2971.727</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>-7950.37</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>1378.489</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>-3673.001</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>-8426.013000000001</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>-4310.779</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B579"/>
+  <dimension ref="A1:B581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6220,6 +6220,26 @@
         <v>-4310.779</v>
       </c>
     </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>-924.967</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>-1300.335</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B581"/>
+  <dimension ref="A1:B583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6240,6 +6240,26 @@
         <v>-1300.335</v>
       </c>
     </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>-1392.132</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>-4223.381</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_etf_flow.xlsx
+++ b/data_cripto/btc_etf_flow.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B583"/>
+  <dimension ref="A1:B588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6260,6 +6260,56 @@
         <v>-4223.381</v>
       </c>
     </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>-3038.073</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>-1504.305</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>-6868.2</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>-8023.662</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>-6174.437</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
